--- a/artfynd/A 52797-2023 artfynd.xlsx
+++ b/artfynd/A 52797-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52797-2023 artfynd.xlsx
+++ b/artfynd/A 52797-2023 artfynd.xlsx
@@ -3282,10 +3282,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119617685</v>
+        <v>119617087</v>
       </c>
       <c r="B26" t="n">
-        <v>91852</v>
+        <v>57326</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3294,41 +3294,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696361</v>
+        <v>696441</v>
       </c>
       <c r="R26" t="n">
-        <v>6644211</v>
+        <v>6644094</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3357,7 +3362,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3367,7 +3372,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3394,10 +3399,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119617087</v>
+        <v>119617685</v>
       </c>
       <c r="B27" t="n">
-        <v>57326</v>
+        <v>91852</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3406,46 +3411,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696441</v>
+        <v>696361</v>
       </c>
       <c r="R27" t="n">
-        <v>6644094</v>
+        <v>6644211</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3511,10 +3511,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119617594</v>
+        <v>119616720</v>
       </c>
       <c r="B28" t="n">
-        <v>100080</v>
+        <v>86205</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3527,34 +3527,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222771</v>
+        <v>3762</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696318</v>
+        <v>696519</v>
       </c>
       <c r="R28" t="n">
-        <v>6644144</v>
+        <v>6643958</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3595,6 +3598,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3613,7 +3617,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119617496</v>
+        <v>119617594</v>
       </c>
       <c r="B29" t="n">
         <v>100080</v>
@@ -3649,14 +3653,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696374</v>
+        <v>696318</v>
       </c>
       <c r="R29" t="n">
-        <v>6644132</v>
+        <v>6644144</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3715,10 +3719,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119616021</v>
+        <v>119617496</v>
       </c>
       <c r="B30" t="n">
-        <v>91852</v>
+        <v>100080</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3731,34 +3735,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>222771</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696372</v>
+        <v>696374</v>
       </c>
       <c r="R30" t="n">
-        <v>6644176</v>
+        <v>6644132</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3817,7 +3821,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119617224</v>
+        <v>119616021</v>
       </c>
       <c r="B31" t="n">
         <v>91852</v>
@@ -3853,14 +3857,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696403</v>
+        <v>696372</v>
       </c>
       <c r="R31" t="n">
-        <v>6644098</v>
+        <v>6644176</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4031,10 +4035,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119617403</v>
+        <v>119617224</v>
       </c>
       <c r="B33" t="n">
-        <v>100080</v>
+        <v>91852</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4047,21 +4051,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222771</v>
+        <v>4366</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4071,10 +4075,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696371</v>
+        <v>696403</v>
       </c>
       <c r="R33" t="n">
-        <v>6644097</v>
+        <v>6644098</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4133,10 +4137,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119616810</v>
+        <v>119617350</v>
       </c>
       <c r="B34" t="n">
-        <v>90067</v>
+        <v>91861</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4149,37 +4153,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>256703</v>
+        <v>5964</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696493</v>
+        <v>696374</v>
       </c>
       <c r="R34" t="n">
-        <v>6643963</v>
+        <v>6644107</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4220,7 +4221,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4239,10 +4239,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119616720</v>
+        <v>119616810</v>
       </c>
       <c r="B35" t="n">
-        <v>86205</v>
+        <v>90067</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4255,21 +4255,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3762</v>
+        <v>256703</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696519</v>
+        <v>696493</v>
       </c>
       <c r="R35" t="n">
-        <v>6643958</v>
+        <v>6643963</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4447,10 +4447,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119617350</v>
+        <v>119617403</v>
       </c>
       <c r="B37" t="n">
-        <v>91861</v>
+        <v>100080</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4463,21 +4463,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696374</v>
+        <v>696371</v>
       </c>
       <c r="R37" t="n">
-        <v>6644107</v>
+        <v>6644097</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 52797-2023 artfynd.xlsx
+++ b/artfynd/A 52797-2023 artfynd.xlsx
@@ -3511,10 +3511,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119616720</v>
+        <v>119616810</v>
       </c>
       <c r="B28" t="n">
-        <v>86205</v>
+        <v>90067</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3527,21 +3527,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3762</v>
+        <v>256703</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696519</v>
+        <v>696493</v>
       </c>
       <c r="R28" t="n">
-        <v>6643958</v>
+        <v>6643963</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3821,10 +3821,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119616021</v>
+        <v>119616720</v>
       </c>
       <c r="B31" t="n">
-        <v>91852</v>
+        <v>86205</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3837,34 +3837,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>3762</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696372</v>
+        <v>696519</v>
       </c>
       <c r="R31" t="n">
-        <v>6644176</v>
+        <v>6643958</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3905,6 +3908,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3923,10 +3927,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119639530</v>
+        <v>119617585</v>
       </c>
       <c r="B32" t="n">
-        <v>90097</v>
+        <v>91861</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3935,41 +3939,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696397</v>
+        <v>696318</v>
       </c>
       <c r="R32" t="n">
-        <v>6644120</v>
+        <v>6644144</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3996,19 +4000,9 @@
           <t>2024-09-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>09:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4035,10 +4029,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119617224</v>
+        <v>119617403</v>
       </c>
       <c r="B33" t="n">
-        <v>91852</v>
+        <v>100080</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4051,21 +4045,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4366</v>
+        <v>222771</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4075,10 +4069,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696403</v>
+        <v>696371</v>
       </c>
       <c r="R33" t="n">
-        <v>6644098</v>
+        <v>6644097</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4137,10 +4131,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119617350</v>
+        <v>119616021</v>
       </c>
       <c r="B34" t="n">
-        <v>91861</v>
+        <v>91852</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4153,34 +4147,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696374</v>
+        <v>696372</v>
       </c>
       <c r="R34" t="n">
-        <v>6644107</v>
+        <v>6644176</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4239,10 +4233,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119616810</v>
+        <v>119639530</v>
       </c>
       <c r="B35" t="n">
-        <v>90067</v>
+        <v>90097</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4251,44 +4245,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>256703</v>
+        <v>5747</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696493</v>
+        <v>696397</v>
       </c>
       <c r="R35" t="n">
-        <v>6643963</v>
+        <v>6644120</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4315,18 +4306,27 @@
           <t>2024-09-08</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-08</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4345,7 +4345,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119617585</v>
+        <v>119617350</v>
       </c>
       <c r="B36" t="n">
         <v>91861</v>
@@ -4381,14 +4381,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696318</v>
+        <v>696374</v>
       </c>
       <c r="R36" t="n">
-        <v>6644144</v>
+        <v>6644107</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4447,10 +4447,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119617403</v>
+        <v>119617224</v>
       </c>
       <c r="B37" t="n">
-        <v>100080</v>
+        <v>91852</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4463,21 +4463,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222771</v>
+        <v>4366</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696371</v>
+        <v>696403</v>
       </c>
       <c r="R37" t="n">
-        <v>6644097</v>
+        <v>6644098</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 52797-2023 artfynd.xlsx
+++ b/artfynd/A 52797-2023 artfynd.xlsx
@@ -3511,10 +3511,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119616810</v>
+        <v>119617594</v>
       </c>
       <c r="B28" t="n">
-        <v>90067</v>
+        <v>100080</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3527,37 +3527,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>256703</v>
+        <v>222771</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696493</v>
+        <v>696318</v>
       </c>
       <c r="R28" t="n">
-        <v>6643963</v>
+        <v>6644144</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3598,7 +3595,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3617,10 +3613,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119617594</v>
+        <v>119616810</v>
       </c>
       <c r="B29" t="n">
-        <v>100080</v>
+        <v>90067</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3633,34 +3629,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222771</v>
+        <v>256703</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696318</v>
+        <v>696493</v>
       </c>
       <c r="R29" t="n">
-        <v>6644144</v>
+        <v>6643963</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,6 +3700,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4131,10 +4131,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119616021</v>
+        <v>119639530</v>
       </c>
       <c r="B34" t="n">
-        <v>91852</v>
+        <v>90097</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4143,41 +4143,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4366</v>
+        <v>5747</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696372</v>
+        <v>696397</v>
       </c>
       <c r="R34" t="n">
-        <v>6644176</v>
+        <v>6644120</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4204,9 +4204,19 @@
           <t>2024-09-08</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4233,10 +4243,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119639530</v>
+        <v>119616021</v>
       </c>
       <c r="B35" t="n">
-        <v>90097</v>
+        <v>91852</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4245,41 +4255,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5747</v>
+        <v>4366</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696397</v>
+        <v>696372</v>
       </c>
       <c r="R35" t="n">
-        <v>6644120</v>
+        <v>6644176</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4306,19 +4316,9 @@
           <t>2024-09-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>09:29</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 52797-2023 artfynd.xlsx
+++ b/artfynd/A 52797-2023 artfynd.xlsx
@@ -3282,10 +3282,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119617087</v>
+        <v>119617685</v>
       </c>
       <c r="B26" t="n">
-        <v>57326</v>
+        <v>91852</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3294,46 +3294,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696441</v>
+        <v>696361</v>
       </c>
       <c r="R26" t="n">
-        <v>6644094</v>
+        <v>6644211</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3362,7 +3357,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3372,7 +3367,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3399,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119617685</v>
+        <v>119617087</v>
       </c>
       <c r="B27" t="n">
-        <v>91852</v>
+        <v>57326</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3411,41 +3406,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696361</v>
+        <v>696441</v>
       </c>
       <c r="R27" t="n">
-        <v>6644211</v>
+        <v>6644094</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3511,10 +3511,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119617594</v>
+        <v>119617350</v>
       </c>
       <c r="B28" t="n">
-        <v>100080</v>
+        <v>91861</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3527,34 +3527,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696318</v>
+        <v>696374</v>
       </c>
       <c r="R28" t="n">
-        <v>6644144</v>
+        <v>6644107</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3613,10 +3613,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119616810</v>
+        <v>119639530</v>
       </c>
       <c r="B29" t="n">
-        <v>90067</v>
+        <v>90097</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3625,44 +3625,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>256703</v>
+        <v>5747</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696493</v>
+        <v>696397</v>
       </c>
       <c r="R29" t="n">
-        <v>6643963</v>
+        <v>6644120</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3689,18 +3686,27 @@
           <t>2024-09-08</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-08</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3719,7 +3725,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119617496</v>
+        <v>119617594</v>
       </c>
       <c r="B30" t="n">
         <v>100080</v>
@@ -3755,14 +3761,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696374</v>
+        <v>696318</v>
       </c>
       <c r="R30" t="n">
-        <v>6644132</v>
+        <v>6644144</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3821,10 +3827,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119616720</v>
+        <v>119616021</v>
       </c>
       <c r="B31" t="n">
-        <v>86205</v>
+        <v>91852</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3837,37 +3843,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3762</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696519</v>
+        <v>696372</v>
       </c>
       <c r="R31" t="n">
-        <v>6643958</v>
+        <v>6644176</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3908,7 +3911,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3927,10 +3929,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119617585</v>
+        <v>119617224</v>
       </c>
       <c r="B32" t="n">
-        <v>91861</v>
+        <v>91852</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3943,34 +3945,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696318</v>
+        <v>696403</v>
       </c>
       <c r="R32" t="n">
-        <v>6644144</v>
+        <v>6644098</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4131,10 +4133,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119639530</v>
+        <v>119617496</v>
       </c>
       <c r="B34" t="n">
-        <v>90097</v>
+        <v>100080</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4143,25 +4145,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5747</v>
+        <v>222771</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4171,13 +4173,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696397</v>
+        <v>696374</v>
       </c>
       <c r="R34" t="n">
-        <v>6644120</v>
+        <v>6644132</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4204,19 +4206,9 @@
           <t>2024-09-08</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>09:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4243,10 +4235,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119616021</v>
+        <v>119616810</v>
       </c>
       <c r="B35" t="n">
-        <v>91852</v>
+        <v>90067</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4259,34 +4251,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4366</v>
+        <v>256703</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696372</v>
+        <v>696493</v>
       </c>
       <c r="R35" t="n">
-        <v>6644176</v>
+        <v>6643963</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4327,6 +4322,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4345,10 +4341,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119617350</v>
+        <v>119616720</v>
       </c>
       <c r="B36" t="n">
-        <v>91861</v>
+        <v>86205</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4361,34 +4357,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696374</v>
+        <v>696519</v>
       </c>
       <c r="R36" t="n">
-        <v>6644107</v>
+        <v>6643958</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4429,6 +4428,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4447,10 +4447,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119617224</v>
+        <v>119617585</v>
       </c>
       <c r="B37" t="n">
-        <v>91852</v>
+        <v>91861</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4463,34 +4463,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696403</v>
+        <v>696318</v>
       </c>
       <c r="R37" t="n">
-        <v>6644098</v>
+        <v>6644144</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 52797-2023 artfynd.xlsx
+++ b/artfynd/A 52797-2023 artfynd.xlsx
@@ -3511,10 +3511,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119617350</v>
+        <v>119617594</v>
       </c>
       <c r="B28" t="n">
-        <v>91861</v>
+        <v>100080</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3527,34 +3527,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696374</v>
+        <v>696318</v>
       </c>
       <c r="R28" t="n">
-        <v>6644107</v>
+        <v>6644144</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119617594</v>
+        <v>119617350</v>
       </c>
       <c r="B30" t="n">
-        <v>100080</v>
+        <v>91861</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3741,34 +3741,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696318</v>
+        <v>696374</v>
       </c>
       <c r="R30" t="n">
-        <v>6644144</v>
+        <v>6644107</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 52797-2023 artfynd.xlsx
+++ b/artfynd/A 52797-2023 artfynd.xlsx
@@ -4552,7 +4552,7 @@
         <v>119618212</v>
       </c>
       <c r="B38" t="n">
-        <v>91861</v>
+        <v>91879</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 52797-2023 artfynd.xlsx
+++ b/artfynd/A 52797-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4668,6 +4668,132 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122319345</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98159</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>696500</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6643939</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52797-2023 artfynd.xlsx
+++ b/artfynd/A 52797-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113295096</v>
+        <v>113304453</v>
       </c>
       <c r="B2" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>937</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söderängsån, Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696251</v>
+        <v>696448</v>
       </c>
       <c r="R2" t="n">
-        <v>6644306</v>
+        <v>6644030</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,6 +747,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,59 +778,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113295105</v>
+        <v>113295577</v>
       </c>
       <c r="B3" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>1106</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söderängsån, Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696251</v>
+        <v>696458</v>
       </c>
       <c r="R3" t="n">
-        <v>6644306</v>
+        <v>6644073</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -863,6 +852,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,37 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113296196</v>
+        <v>113297665</v>
       </c>
       <c r="B4" t="n">
-        <v>91626</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696525</v>
+        <v>696471</v>
       </c>
       <c r="R4" t="n">
-        <v>6643949</v>
+        <v>6644106</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -967,6 +956,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,15 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113295788</v>
+        <v>113295270</v>
       </c>
       <c r="B5" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +998,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696493</v>
+        <v>696408</v>
       </c>
       <c r="R5" t="n">
-        <v>6644000</v>
+        <v>6644172</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1070,6 +1059,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,15 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113295750</v>
+        <v>113295924</v>
       </c>
       <c r="B6" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,43 +1101,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696490</v>
+        <v>696564</v>
       </c>
       <c r="R6" t="n">
-        <v>6644050</v>
+        <v>6644005</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1183,13 +1164,17 @@
           <t>2023-11-18</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Skogen är avverkningsanmäld</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1208,15 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113295270</v>
+        <v>119616720</v>
       </c>
       <c r="B7" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,38 +1204,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3215</v>
+        <v>3762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696408</v>
+        <v>696519</v>
       </c>
       <c r="R7" t="n">
-        <v>6644172</v>
+        <v>6643958</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1279,17 +1261,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Skogen är avverkningsanmäld</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1298,6 +1275,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1316,15 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113311155</v>
+        <v>113310961</v>
       </c>
       <c r="B8" t="n">
-        <v>100812</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1305,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>3884</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696361</v>
+        <v>696500</v>
       </c>
       <c r="R8" t="n">
-        <v>6644211</v>
+        <v>6643939</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,61 +1395,55 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113310961</v>
+        <v>119616021</v>
       </c>
       <c r="B9" t="n">
-        <v>90885</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3884</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696500</v>
+        <v>696372</v>
       </c>
       <c r="R9" t="n">
-        <v>6643939</v>
+        <v>6644176</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1500,22 +1467,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:57</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:57</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,66 +1487,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113295924</v>
+        <v>119617224</v>
       </c>
       <c r="B10" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696564</v>
+        <v>696403</v>
       </c>
       <c r="R10" t="n">
-        <v>6644005</v>
+        <v>6644098</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1613,17 +1564,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Skogen är avverkningsanmäld</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,54 +1596,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113487582</v>
+        <v>119617685</v>
       </c>
       <c r="B11" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro , Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696395</v>
+        <v>696361</v>
       </c>
       <c r="R11" t="n">
-        <v>6644151</v>
+        <v>6644211</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1721,12 +1661,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,63 +1691,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113295559</v>
+        <v>113760271</v>
       </c>
       <c r="B12" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696461</v>
+        <v>696395</v>
       </c>
       <c r="R12" t="n">
-        <v>6644054</v>
+        <v>6644151</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1827,14 +1774,19 @@
           <t>2023-11-18</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-18</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Skogen är avverkningsanmäld</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,6 +1795,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1861,15 +1814,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113304453</v>
+        <v>113295559</v>
       </c>
       <c r="B13" t="n">
-        <v>89896</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,21 +1825,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>937</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,13 +1850,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696448</v>
+        <v>696461</v>
       </c>
       <c r="R13" t="n">
-        <v>6644030</v>
+        <v>6644054</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1969,37 +1917,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113298288</v>
+        <v>113297412</v>
       </c>
       <c r="B14" t="n">
-        <v>100812</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221235</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2010,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696369</v>
+        <v>696459</v>
       </c>
       <c r="R14" t="n">
-        <v>6644204</v>
+        <v>6643971</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2077,54 +2020,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113295736</v>
+        <v>119639530</v>
       </c>
       <c r="B15" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>5747</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696474</v>
+        <v>696397</v>
       </c>
       <c r="R15" t="n">
-        <v>6644037</v>
+        <v>6644120</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2148,17 +2085,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Skogen är avverkningsanmäld</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2185,15 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113295553</v>
+        <v>113296196</v>
       </c>
       <c r="B16" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2201,21 +2138,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2226,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696474</v>
+        <v>696525</v>
       </c>
       <c r="R16" t="n">
-        <v>6644037</v>
+        <v>6643949</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2262,11 +2199,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,54 +2225,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113295925</v>
+        <v>119617350</v>
       </c>
       <c r="B17" t="n">
-        <v>97684</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219874</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696564</v>
+        <v>696374</v>
       </c>
       <c r="R17" t="n">
-        <v>6644005</v>
+        <v>6644107</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2364,17 +2290,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Skogen är avverkningsanmäld</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,15 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113295385</v>
+        <v>119617585</v>
       </c>
       <c r="B18" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,38 +2333,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696421</v>
+        <v>696318</v>
       </c>
       <c r="R18" t="n">
-        <v>6644147</v>
+        <v>6644144</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,17 +2387,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Skogen är avverkningsanmäld</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,15 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113297665</v>
+        <v>119618212</v>
       </c>
       <c r="B19" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,38 +2430,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696471</v>
+        <v>696347</v>
       </c>
       <c r="R19" t="n">
-        <v>6644106</v>
+        <v>6644179</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2580,17 +2493,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Skogen är avverkningsanmäld</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,27 +2523,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113298588</v>
+        <v>113295100</v>
       </c>
       <c r="B20" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2633,41 +2546,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696204</v>
+        <v>696251</v>
       </c>
       <c r="R20" t="n">
-        <v>6644289</v>
+        <v>6644306</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2705,7 +2618,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2724,15 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113488492</v>
+        <v>119617087</v>
       </c>
       <c r="B21" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2740,38 +2647,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro , Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696185</v>
+        <v>696441</v>
       </c>
       <c r="R21" t="n">
-        <v>6644295</v>
+        <v>6644094</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2795,12 +2706,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,44 +2736,39 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113295100</v>
+        <v>113295105</v>
       </c>
       <c r="B22" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2861,13 +2777,18 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro, Upl</t>
+          <t>Söderängsån, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -2877,7 +2798,7 @@
         <v>6644306</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2915,6 +2836,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2933,37 +2855,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113496125</v>
+        <v>113295750</v>
       </c>
       <c r="B23" t="n">
-        <v>5348</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101728</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2978,17 +2895,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro, Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696468</v>
+        <v>696490</v>
       </c>
       <c r="R23" t="n">
-        <v>6644037</v>
+        <v>6644050</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3015,19 +2932,9 @@
           <t>2023-11-18</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:44</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,53 +2962,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113295577</v>
+        <v>113298476</v>
       </c>
       <c r="B24" t="n">
-        <v>90532</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1106</v>
+        <v>219711</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Naturskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696458</v>
+        <v>696242</v>
       </c>
       <c r="R24" t="n">
-        <v>6644073</v>
+        <v>6644217</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3147,7 +3047,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3166,15 +3065,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113760271</v>
+        <v>113298477</v>
       </c>
       <c r="B25" t="n">
-        <v>90735</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,37 +3076,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5420</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro  (Kalkbarrskog sydost om Edsbro ), Upl</t>
+          <t>Naturskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696395</v>
+        <v>696242</v>
       </c>
       <c r="R25" t="n">
-        <v>6644151</v>
+        <v>6644217</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3242,19 +3134,14 @@
           <t>2023-11-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-11-18</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:18</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,7 +3150,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3282,15 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119617685</v>
+        <v>113295925</v>
       </c>
       <c r="B26" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3298,37 +3179,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>219874</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696361</v>
+        <v>696564</v>
       </c>
       <c r="R26" t="n">
-        <v>6644211</v>
+        <v>6644005</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3352,22 +3234,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3382,70 +3259,61 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119617087</v>
+        <v>113295788</v>
       </c>
       <c r="B27" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696441</v>
+        <v>696493</v>
       </c>
       <c r="R27" t="n">
-        <v>6644094</v>
+        <v>6644000</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3469,22 +3337,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3499,65 +3357,70 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119617594</v>
+        <v>113297423</v>
       </c>
       <c r="B28" t="n">
-        <v>100080</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696318</v>
+        <v>696459</v>
       </c>
       <c r="R28" t="n">
-        <v>6644144</v>
+        <v>6643971</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3581,12 +3444,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3613,53 +3481,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119639530</v>
+        <v>113298288</v>
       </c>
       <c r="B29" t="n">
-        <v>90097</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5747</v>
+        <v>221235</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696397</v>
+        <v>696369</v>
       </c>
       <c r="R29" t="n">
-        <v>6644120</v>
+        <v>6644204</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3683,22 +3547,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3725,53 +3584,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119617350</v>
+        <v>113311155</v>
       </c>
       <c r="B30" t="n">
-        <v>91861</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696374</v>
+        <v>696361</v>
       </c>
       <c r="R30" t="n">
-        <v>6644107</v>
+        <v>6644211</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3795,12 +3650,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3815,27 +3680,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119616021</v>
+        <v>113295096</v>
       </c>
       <c r="B31" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3843,37 +3703,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Söderängsån, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696372</v>
+        <v>696251</v>
       </c>
       <c r="R31" t="n">
-        <v>6644176</v>
+        <v>6644306</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3897,12 +3758,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3929,15 +3790,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119617224</v>
+        <v>113295736</v>
       </c>
       <c r="B32" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3945,37 +3801,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696403</v>
+        <v>696474</v>
       </c>
       <c r="R32" t="n">
-        <v>6644098</v>
+        <v>6644037</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3999,12 +3856,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4031,15 +3893,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119617403</v>
+        <v>113298588</v>
       </c>
       <c r="B33" t="n">
-        <v>100080</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4047,37 +3904,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696371</v>
+        <v>696204</v>
       </c>
       <c r="R33" t="n">
-        <v>6644097</v>
+        <v>6644289</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4101,12 +3962,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4115,6 +3976,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4133,15 +3995,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119617496</v>
+        <v>113487582</v>
       </c>
       <c r="B34" t="n">
-        <v>100080</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4149,37 +4006,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696374</v>
+        <v>696395</v>
       </c>
       <c r="R34" t="n">
-        <v>6644132</v>
+        <v>6644151</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4203,12 +4061,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4235,15 +4093,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119616810</v>
+        <v>113488492</v>
       </c>
       <c r="B35" t="n">
-        <v>90067</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4251,40 +4104,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>256703</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696493</v>
+        <v>696185</v>
       </c>
       <c r="R35" t="n">
-        <v>6643963</v>
+        <v>6644295</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4308,12 +4159,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4322,7 +4173,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4341,15 +4191,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119616720</v>
+        <v>119617403</v>
       </c>
       <c r="B36" t="n">
-        <v>86205</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4357,37 +4202,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3762</v>
+        <v>222771</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696519</v>
+        <v>696371</v>
       </c>
       <c r="R36" t="n">
-        <v>6643958</v>
+        <v>6644097</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4428,7 +4270,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4447,15 +4288,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119617585</v>
+        <v>119617496</v>
       </c>
       <c r="B37" t="n">
-        <v>91861</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4463,34 +4299,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Kalkbarrskog sydost om Edsbro , Kalkbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696318</v>
+        <v>696374</v>
       </c>
       <c r="R37" t="n">
-        <v>6644144</v>
+        <v>6644132</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4549,15 +4385,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119618212</v>
+        <v>119617594</v>
       </c>
       <c r="B38" t="n">
-        <v>91879</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4565,43 +4396,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5964</v>
+        <v>222771</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696347</v>
+        <v>696318</v>
       </c>
       <c r="R38" t="n">
-        <v>6644179</v>
+        <v>6644144</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4631,19 +4453,9 @@
           <t>2024-09-08</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4658,15 +4470,116 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>119616810</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Naturbarrskog sydost om Edsbro , Naturbarrskog sydost om Edsbro , Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>696493</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6643963</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52797-2023 artfynd.xlsx
+++ b/artfynd/A 52797-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113304453</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113295577</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113297665</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113295270</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113295924</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,6 +1321,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119616720</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113310961</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119616021</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1593,6 +1638,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119617224</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119617685</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1811,6 +1866,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113760271</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1914,6 +1974,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113295559</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2017,6 +2082,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113297412</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2124,6 +2194,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119639530</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2222,6 +2297,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113296196</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2319,6 +2399,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119617350</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2416,6 +2501,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119617585</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2532,6 +2622,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119618212</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2633,6 +2728,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113295100</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2745,6 +2845,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119617087</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2852,6 +2957,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113295105</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2959,6 +3069,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113295750</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3062,6 +3177,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113298476</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3165,6 +3285,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113298477</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3268,6 +3393,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113295925</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3366,6 +3496,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113295788</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3478,6 +3613,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113297423</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3581,6 +3721,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113298288</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3689,6 +3834,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113311155</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3787,6 +3937,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113295096</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3890,6 +4045,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113295736</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3992,6 +4152,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113298588</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4090,6 +4255,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113487582</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4188,6 +4358,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113488492</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4285,6 +4460,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119617403</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4382,6 +4562,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119617496</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4479,6 +4664,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119617594</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4580,8 +4770,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119616810</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>